--- a/docs/03_詳細設計/04_クラス・内部IF設計/KF-DD-005_クラス設計書.xlsx
+++ b/docs/03_詳細設計/04_クラス・内部IF設計/KF-DD-005_クラス設計書.xlsx
@@ -642,7 +642,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
     <row r="15">
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>ONL-001〜022 と BAT-001〜003 の規格 JSON から自動集約した総覧。クラス単位の詳細は領域別 KF-DD-CLS を参照。v2.1 は ONL-022（申請提出）関連クラスの追加、バッチ領域 09 の新設、更新済み規格の反映。</t>
+          <t>ONL-001〜023 と BAT-001〜003 の規格 JSON から自動集約した総覧。クラス単位の詳細は領域別 KF-DD-CLS を参照。v2.2 は実装反映（ONL-023 パスワード変更の ChangePasswordRequest、BootstrapAdminInitializer の追加。RestAuthenticationEntryPoint / RestAccessDeniedHandler は専用クラスを作らず SecurityConfig のラムダに変更したため削除）。</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -794,7 +794,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="49" customHeight="1">
+    <row r="4" ht="19" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ErrorResponse</t>
@@ -812,7 +812,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>GlobalExceptionHandler、RestAccessDeniedHandler、RestAuthenticationEntryPoint</t>
+          <t>GlobalExceptionHandler</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="19" customHeight="1">
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SecurityConfig</t>
@@ -873,7 +873,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>認証・認可・BCrypt・JWT・CORS の Bean 定義</t>
+          <t>認証・認可・BCrypt・JWT・CORS の Bean 定義。401 / 403 の JSON 応答（writeError）を含む</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>JWT 発行</t>
+          <t>JWT 発行（有効 2 時間）</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>users のメール検索</t>
+          <t>users のメール検索 findByEmail</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>ApprovalRouteService、ApprovalService、AuthService、DevDataInitializer、LeaveBalanceService、LeaveGrantService、LeaveGrantUni…</t>
+          <t>ApprovalRouteService、ApprovalService、AuthService、BootstrapAdminInitializer、DevDataInitializer、LeaveBalanceService、Leave…</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="34" customHeight="1">
+    <row r="16" ht="64" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>EmailNormalizer</t>
@@ -1071,29 +1071,29 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>メールアドレスの正規化 normalize（trim＋小文字化）。保存時・検索時に共通利用（ONL-014 も使用）</t>
+          <t>【未実装・設計案】メールアドレスの正規化 normalize（trim＋小文字化）。現行コードは AuthService#login 内で trim().toLowerCase(Locale.ROOT) を直接実行しており、ONL-014（ユーザー管理）の実装時に共通化する予定</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>AuthService、UserService</t>
+          <t>UserService</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>RestAuthenticationEntryPoint</t>
+          <t>BootstrapAdminInitializer</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Config</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>未認証・トークン不正・期限切れを 401 / E-001 の JSON で返す</t>
+          <t>初期管理者（ADMIN）1 名の作成（@Order(2)。users が空かつ bootstrap 設定が揃っているときのみ）</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1105,22 +1105,22 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>RestAccessDeniedHandler</t>
+          <t>ChangePasswordRequest</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>DTO</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>フィルタ段階の権限不足を 403 / E-010 の JSON で返す</t>
+          <t>リクエスト（currentPassword / newPassword）と入力チェック定義</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AuthController、AuthService</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>jdbc:postgresql://localhost:5432/kintaiflow</t>
+          <t>jdbc:postgresql://localhost:5432/kintaiflow（compose では環境変数 SPRING_DATASOURCE_URL で db コンテナへ）</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
     </row>
-    <row r="26" ht="34" customHeight="1">
+    <row r="26" ht="64" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>spring.datasource.password</t>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>application-local.properties</t>
+          <t>application-local.properties／環境変数 SPRING_DATASOURCE_PASSWORD</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1262,32 +1262,32 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="34" customHeight="1">
+    <row r="27" ht="64" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.jwt.secret</t>
+          <t>spring.flyway.enabled / baseline-on-migrate / baseline-version</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>application-local.properties</t>
+          <t>application.properties</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>JWT 署名鍵（Base64、32バイト以上）</t>
+          <t>true / true / 1。DB は Flyway（db/migration/V1__init_schema.sql）が作成する。旧 schema.sql で作成済みの DB は V1 適用済みとして取り込む</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Git 管理外</t>
+          <t>V1 は書き換えない。変更は V2__*.sql を追加（KF-DD-006）。旧 DB に users の新 4 列が無い場合は validate で起動失敗するため reset-dev.sql で作り直す</t>
         </is>
       </c>
     </row>
     <row r="28" ht="34" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.jwt.expiration-hours</t>
+          <t>spring.jpa.hibernate.ddl-auto</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -1297,900 +1297,1112 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>トークン有効時間（時間）。8</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>変更時は本書と KF-DD-001 を改訂</t>
-        </is>
-      </c>
+          <t>validate（Entity と DB の整合を起動時に検証するだけ。DDL は自動生成しない）</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
     </row>
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>spring.datasource.hikari.connection-init-sql</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>application.properties</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>SET TIME ZONE 'Asia/Tokyo'（DB セッションの時刻を JST に固定。locked_until 等の壁時計時刻と整合させる）</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="94" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>kintaiflow.jwt.secret</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>application-local.properties／環境変数 KINTAIFLOW_JWT_SECRET（compose では .env の JWT_SECRET）</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>JWT 署名鍵（Base64、32バイト以上）</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Git 管理外</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>kintaiflow.jwt.expiration-hours</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>application.properties</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>トークン有効時間（時間）。2</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>変更時は本書・KF-DD-006・KF-BD-010 を改訂</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="109" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
           <t>kintaiflow.dev.seed-password</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>application-local.properties</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>開発用ユーザーの初期パスワード</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>未設定ならユーザー投入しない。Git 管理外</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>spring.jpa.properties.hibernate.jdbc.time_zone</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>application.properties</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Asia/Tokyo</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Timestamp 型の JDBC 変換を JST に固定</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="49" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>spring.datasource.hikari.connection-init-sql</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>application.properties</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>SET TIME ZONE 'Asia/Tokyo'</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>DB セッションを JST にし、created_at / updated_at の DEFAULT CURRENT_TIMESTAMP も JST にする</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>（Bean）Clock</t>
-        </is>
-      </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>config/ClockConfig.java</t>
+          <t>application-local.properties／環境変数 KINTAIFLOW_DEV_SEED_PASSWORD（compose では .env の DEV_SEED_PASSWORD）</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Clock.system(Asia/Tokyo)</t>
+          <t>開発用ユーザー 100 名の初期パスワード</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>業務時刻はこの Bean 経由でのみ取得する</t>
+          <t>未設定（本番）ならユーザー投入しない。Git 管理外</t>
         </is>
       </c>
     </row>
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>（定数）STANDARD_MINUTES</t>
+          <t>kintaiflow.cors.allowed-origins</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>AttendanceCalculator</t>
+          <t>application.properties</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>許可オリジン（カンマ区切り）。既定 http://localhost:5173</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>所定労働時間（分）。変更時は本書と KF-DD-001 を改訂</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="34" customHeight="1">
+          <t>本番は画面の URL に合わせる（Docker 構成は同一オリジン経由のため通常不要）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="94" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>（定数）BREAK_OVER_6H / BREAK_OVER_8H</t>
+          <t>kintaiflow.bootstrap.admin-email</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>AttendanceCalculator</t>
+          <t>環境変数 KINTAIFLOW_BOOTSTRAP_ADMIN_EMAIL（compose では .env の BOOTSTRAP_ADMIN_EMAIL）</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>45 / 60</t>
+          <t>初期管理者のメールアドレス</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>休憩控除（分）。しきい値は 360 / 480 分</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="34" customHeight="1">
+          <t>未設定なら初期管理者を作らない。Git 管理外（.env）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="94" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>spring.jackson.default-property-inclusion</t>
+          <t>kintaiflow.bootstrap.admin-password</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
+          <t>環境変数 KINTAIFLOW_BOOTSTRAP_ADMIN_PASSWORD（compose では .env の BOOTSTRAP_ADMIN_PASSWORD）</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>初期管理者の初期パスワード（12 文字以上・英字と数字を含む）</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>ポリシー違反なら起動失敗。Git 管理外（.env）。初回ログイン後に変更させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>management.endpoints.web.exposure.include</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
           <t>application.properties</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>指定しない（既定 ALWAYS）</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>null の項目も JSON に出力するため non_null にしない</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="49" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>JVM オプション user.timezone</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>起動オプション / 環境変数 JAVA_TOOL_OPTIONS</t>
-        </is>
-      </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>-Duser.timezone=Asia/Tokyo</t>
+          <t>health（/actuator/health を公開。認証不要。management.endpoint.health.probes.enabled=true）</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>サーバー時刻（now）の基準を JST に揃える</t>
+          <t>Docker のヘルスチェック・監視用</t>
         </is>
       </c>
     </row>
     <row r="37" ht="34" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>MAX_PERIOD_DAYS</t>
+          <t>spring.jpa.properties.hibernate.jdbc.time_zone</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>RequestService の定数</t>
+          <t>application.properties</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1100（休暇の最大期間・日）</t>
+          <t>Asia/Tokyo</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>変更時は本書の 4.1 を改訂</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="49" customHeight="1">
+          <t>Timestamp 型の JDBC 変換を JST に固定</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>（Bean）Clock / AppTime</t>
+          <t>（Bean）Clock</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>config/ClockConfig.java・AppTime.java</t>
+          <t>config/ClockConfig.java</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>日時の ISO 8601（+09:00）変換は AppTime.toIso を使う</t>
+          <t>Clock.system(Asia/Tokyo)</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>ONL-002 で定義済み。新規設定なし</t>
+          <t>業務時刻はこの Bean 経由でのみ取得する</t>
         </is>
       </c>
     </row>
     <row r="39" ht="34" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>（コード定数）LeaveType.ANNUAL_LEAVE_NAME</t>
+          <t>（定数）STANDARD_MINUTES</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>entity/LeaveType.java</t>
+          <t>AttendanceCalculator</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>年次有給休暇</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>schema.sql の初期データと一致させる</t>
+          <t>所定労働時間（分）。変更時は本書と KF-DD-001 を改訂</t>
         </is>
       </c>
     </row>
     <row r="40" ht="34" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>（コード定数）FIVE / TEN</t>
+          <t>（定数）BREAK_OVER_6H / BREAK_OVER_8H</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>LeaveBalanceService</t>
+          <t>AttendanceCalculator</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>年5日義務の日数 5.0 / 対象となる付与日数 10</t>
+          <t>45 / 60</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>法改正時はコード修正</t>
+          <t>休憩控除（分）。しきい値は 360 / 480 分</t>
         </is>
       </c>
     </row>
     <row r="41" ht="34" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>（コード定数）MAX_CHAIN_DEPTH</t>
+          <t>spring.jackson.default-property-inclusion</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>UserService</t>
+          <t>application.properties</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>100（上長の連鎖を辿る最大段数）</t>
+          <t>指定しない（既定 ALWAYS）</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>データ破損時の無限ループ防止</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="34" customHeight="1">
+          <t>null の項目も JSON に出力するため non_null にしない</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="49" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>（コード定数）YEAR_MIN / YEAR_MAX</t>
+          <t>JVM オプション user.timezone</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>HolidayService</t>
+          <t>起動オプション / 環境変数 JAVA_TOOL_OPTIONS</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2000 / 2099</t>
+          <t>-Duser.timezone=Asia/Tokyo</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>年の入力範囲</t>
+          <t>サーバー時刻（now）の基準を JST に揃える</t>
         </is>
       </c>
     </row>
     <row r="43" ht="34" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>spring.jpa.properties.jakarta.persistence.lock.timeout</t>
+          <t>MAX_PERIOD_DAYS</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>application.properties</t>
+          <t>RequestService の定数</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>悲観ロックの待ち時間（ミリ秒）。5000 を推奨</t>
+          <t>1100（休暇の最大期間・日）</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>超過時は E-012（500）</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="34" customHeight="1">
+          <t>変更時は本書の 4.1 を改訂</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="49" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>(JST の扱い)</t>
+          <t>（Bean）Clock / AppTime</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>config/ClockConfig（ONL-013）</t>
+          <t>config/ClockConfig.java・AppTime.java</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Clock Bean（ZoneId Asia/Tokyo）を LeaveBalanceService にコンストラクタ注入</t>
+          <t>日時の ISO 8601（+09:00）変換は AppTime.toIso を使う</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>本日の判定はすべて LocalDate.now(clock)。サーバ TZ に依存させない</t>
+          <t>ONL-002 で定義済み。新規設定なし</t>
         </is>
       </c>
     </row>
     <row r="45" ht="34" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>(設定値なし)</t>
+          <t>（コード定数）LeaveType.ANNUAL_LEAVE_NAME</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>entity/LeaveType.java</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>本処理専用の設定値はない</t>
+          <t>年次有給休暇</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>ファイル名・BOM・列定義は ReportService の定数</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="49" customHeight="1">
+          <t>schema.sql の初期データと一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="34" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>（定数）一覧の最大件数 50</t>
+          <t>（コード定数）FIVE / TEN</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>NotificationRepository のメソッド名（Top50）</t>
+          <t>LeaveBalanceService</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>年5日義務の日数 5.0 / 対象となる付与日数 10</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>変更時はメソッド名・本書・KF-DD-001 を改訂</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="19" customHeight="1">
+          <t>法改正時はコード修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="34" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>（なし）</t>
+          <t>（コード定数）MAX_CHAIN_DEPTH</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UserService</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>本処理固有の設定値はない</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr"/>
+          <t>100（上長の連鎖を辿る最大段数）</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>データ破損時の無限ループ防止</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="34" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.leave-grant.cron</t>
+          <t>（コード定数）YEAR_MIN / YEAR_MAX</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>0 0 2 * * *</t>
+          <t>HolidayService</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>BAT-001 の実行契機（Spring の 6 項目 cron: 秒 分 時 日 月 曜日）</t>
+          <t>2000 / 2099</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>zone と組み合わせて評価</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="19" customHeight="1">
+          <t>年の入力範囲</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="34" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.zone</t>
+          <t>spring.jpa.properties.jakarta.persistence.lock.timeout</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Asia/Tokyo</t>
+          <t>application.properties</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>@Scheduled の zone。3 バッチ共通</t>
+          <t>悲観ロックの待ち時間（ミリ秒）。5000 を推奨</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>サーバ TZ に依存しない</t>
+          <t>超過時は E-012（500）</t>
         </is>
       </c>
     </row>
     <row r="50" ht="34" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.leave-grant.catch-up-days</t>
+          <t>(JST の扱い)</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>config/ClockConfig（ONL-013）</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>取りこぼし救済の遡り日数</t>
+          <t>Clock Bean（ZoneId Asia/Tokyo）を LeaveBalanceService にコンストラクタ注入</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0 で当日のみ</t>
+          <t>本日の判定はすべて LocalDate.now(clock)。サーバ TZ に依存させない</t>
         </is>
       </c>
     </row>
     <row r="51" ht="34" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.scheduling-enabled</t>
+          <t>(設定値なし)</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>false で @EnableScheduling を無効化（テスト・run-once・2台目インスタンス）</t>
+          <t>本処理専用の設定値はない</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>3 バッチ共通</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="34" customHeight="1">
+          <t>ファイル名・BOM・列定義は ReportService の定数</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="49" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.run-once</t>
+          <t>（定数）一覧の最大件数 50</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>(未設定)</t>
+          <t>NotificationRepository のメソッド名（Top50）</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>BAT-001 / BAT-002 / BAT-003 のいずれか。設定時のみ BatchRunOnceRunner が有効</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>手動実行用（8.6）</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="34" customHeight="1">
+          <t>変更時はメソッド名・本書・KF-DD-001 を改訂</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="19" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.target-date</t>
+          <t>（なし）</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>(未設定)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>run-once の判定基準日（yyyy-MM-dd）</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>未設定は本日(JST)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="34" customHeight="1">
+          <t>本処理固有の設定値はない</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54" ht="49" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>spring.task.scheduling.pool.size</t>
+          <t>MIN_PASSWORD_LENGTH</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>AuthService（定数 static final int）</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>スケジューラのスレッド数（BAT 同士が待ち合わせにならないように）</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>既定は 1</t>
+          <t>変更時は本書・KF-BD-010・KF-RD-002 §4・SCR-007 のヒント文言（12文字以上）を改訂</t>
         </is>
       </c>
     </row>
     <row r="55" ht="49" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>spring.task.scheduling.shutdown.await-termination / -period</t>
+          <t>@Size(max=72)</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>true / 60s</t>
+          <t>ChangePasswordRequest#newPassword</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>停止時に実行中のバッチ完了を待つ</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>BCrypt の入力上限（72 バイト）に合わせた文字数上限</t>
         </is>
       </c>
     </row>
     <row r="56" ht="34" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.mandatory-alert.cron</t>
+          <t>PasswordEncoder</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>0 0 3 1 * *</t>
+          <t>SecurityConfig#passwordEncoder</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>BAT-002 の実行契機（毎月1日 03:00）</t>
+          <t>BCryptPasswordEncoder（強度は既定値）</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>BAT-001（02:00）の完了後</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="34" customHeight="1">
+          <t>ONL-001 と共通。ログイン照合・初期ユーザー作成・本処理で同じ Bean を使う</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="49" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.mandatory-alert.threshold-days</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>AuthService（定数 ZoneId.of("Asia/Tokyo")）</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>義務日数</t>
+          <t>password_changed_at の時刻基準</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>@ConfigurationProperties 化してもよい</t>
+          <t>DB セッションも hikari.connection-init-sql で JST に固定（ONL-001 7.3）</t>
         </is>
       </c>
     </row>
     <row r="58" ht="34" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.mandatory-alert.elapsed-months</t>
+          <t>kintaiflow.batch.leave-grant.cron</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0 0 2 * * *</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>通知開始の経過月数</t>
+          <t>BAT-001 の実行契機（Spring の 6 項目 cron: 秒 分 時 日 月 曜日）</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>D-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="34" customHeight="1">
+          <t>zone と組み合わせて評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="19" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.mandatory-alert.min-granted-days</t>
+          <t>kintaiflow.batch.zone</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Asia/Tokyo</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>対象の付与日数下限（ONL-013 の TEN と同値）</t>
+          <t>@Scheduled の zone。3 バッチ共通</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>D-1。findAlertBaseRows の TEN は ONL-013 側の定数</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="49" customHeight="1">
+          <t>サーバ TZ に依存しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="34" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.zone / scheduling-enabled / run-once / target-date</t>
+          <t>kintaiflow.batch.leave-grant.catch-up-days</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>(BAT-001 書 7.3 を参照)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>共通設定</t>
+          <t>取りこぼし救済の遡り日数</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 で当日のみ</t>
         </is>
       </c>
     </row>
     <row r="61" ht="34" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.backup.cron</t>
+          <t>kintaiflow.batch.scheduling-enabled</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>0 30 3 * * *</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>実行契機（毎日 03:30）</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr"/>
-    </row>
-    <row r="62" ht="19" customHeight="1">
+          <t>false で @EnableScheduling を無効化（テスト・run-once・2台目インスタンス）</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>3 バッチ共通</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="34" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.backup.dir</t>
+          <t>kintaiflow.batch.run-once</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>backup</t>
+          <t>(未設定)</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>保存先</t>
+          <t>BAT-001 / BAT-002 / BAT-003 のいずれか。設定時のみ BatchRunOnceRunner が有効</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>本番は絶対パス・DB と別ディスク推奨</t>
+          <t>手動実行用（8.6）</t>
         </is>
       </c>
     </row>
     <row r="63" ht="34" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.backup.file-prefix</t>
+          <t>kintaiflow.batch.target-date</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>kintai_</t>
+          <t>(未設定)</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>ファイル名接頭辞</t>
+          <t>run-once の判定基準日（yyyy-MM-dd）</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>世代判定に使用</t>
+          <t>未設定は本日(JST)</t>
         </is>
       </c>
     </row>
     <row r="64" ht="34" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.backup.retention</t>
+          <t>spring.task.scheduling.pool.size</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>保持世代数（≧1）</t>
+          <t>スケジューラのスレッド数（BAT 同士が待ち合わせにならないように）</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>KF-BD-010</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="34" customHeight="1">
+          <t>既定は 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="49" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.backup.pg-dump-path</t>
+          <t>spring.task.scheduling.shutdown.await-termination / -period</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>pg_dump</t>
+          <t>true / 60s</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>実行ファイル</t>
+          <t>停止時に実行中のバッチ完了を待つ</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>例 /usr/lib/postgresql/18/bin/pg_dump</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="94" customHeight="1">
+          <t>D-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="34" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.backup.db-host / db-port / db-name / db-user</t>
+          <t>kintaiflow.batch.mandatory-alert.cron</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>${DB_HOST:localhost} / ${DB_PORT:5432} / ${DB_NAME:kintaiflow} / ${DB_USER:kintai}</t>
+          <t>0 0 3 1 * *</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>接続先（環境変数から展開）</t>
+          <t>BAT-002 の実行契機（毎月1日 03:00）</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>spring.datasource と同じ環境変数を使い二重管理しない</t>
+          <t>BAT-001（02:00）の完了後</t>
         </is>
       </c>
     </row>
     <row r="67" ht="34" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.backup.db-password</t>
+          <t>kintaiflow.batch.mandatory-alert.threshold-days</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>${DB_PASSWORD}</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>パスワード（既定なし）。環境変数のみ。application.properties に平文で書かない</t>
+          <t>義務日数</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>ログ・引数・toString 禁止</t>
+          <t>@ConfigurationProperties 化してもよい</t>
         </is>
       </c>
     </row>
     <row r="68" ht="34" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.backup.timeout-seconds</t>
+          <t>kintaiflow.batch.mandatory-alert.elapsed-months</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>pg_dump の最大実行時間</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr"/>
+          <t>通知開始の経過月数</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>D-2</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="34" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
+          <t>kintaiflow.batch.mandatory-alert.min-granted-days</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>対象の付与日数下限（ONL-013 の TEN と同値）</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>D-1。findAlertBaseRows の TEN は ONL-013 側の定数</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="49" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>kintaiflow.batch.zone / scheduling-enabled / run-once / target-date</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>(BAT-001 書 7.3 を参照)</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>共通設定</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="34" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>kintaiflow.batch.backup.cron</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>0 30 3 * * *</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>実行契機（毎日 03:30）</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72" ht="19" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>kintaiflow.batch.backup.dir</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>backup</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>保存先</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>本番は絶対パス・DB と別ディスク推奨</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="34" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>kintaiflow.batch.backup.file-prefix</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>kintai_</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>ファイル名接頭辞</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>世代判定に使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="34" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>kintaiflow.batch.backup.retention</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>保持世代数（≧1）</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>KF-BD-010</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="34" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>kintaiflow.batch.backup.pg-dump-path</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>pg_dump</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>実行ファイル</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>例 /usr/lib/postgresql/18/bin/pg_dump</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="94" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>kintaiflow.batch.backup.db-host / db-port / db-name / db-user</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>${DB_HOST:localhost} / ${DB_PORT:5432} / ${DB_NAME:kintaiflow} / ${DB_USER:kintai}</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>接続先（環境変数から展開）</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>spring.datasource と同じ環境変数を使い二重管理しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="34" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>kintaiflow.batch.backup.db-password</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>${DB_PASSWORD}</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>パスワード（既定なし）。環境変数のみ。application.properties に平文で書かない</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>ログ・引数・toString 禁止</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="34" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>kintaiflow.batch.backup.timeout-seconds</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>pg_dump の最大実行時間</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr"/>
+    </row>
+    <row r="79" ht="34" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
           <t>kintaiflow.batch.backup.min-size-bytes</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>成功とみなす最小サイズ</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr"/>
+      <c r="D79" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2306,7 +2518,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>E-001〜E-016（本システム全体で一意）。</t>
+          <t>E-001〜E-018（本システム全体で一意）。</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2416,6 +2628,29 @@
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="79" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/04</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>実装反映（逆反映）：ChangePasswordRequest（ONL-023）と BootstrapAdminInitializer を追加。RestAuthenticationEntryPoint / RestAccessDeniedHandler は専用クラスを作らず SecurityConfig のラムダに変更したため削除（126 クラスのまま）。EmailNormalizer は『未実装（設計のみ）』と明記</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2477,12 +2712,12 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
           <t>SecurityConfig、ClockConfig、AppTime、DevDataInitializer、SchedulingConfig
-AppTime、BackupProperties、ClockConfig、DevDataInitializer、SchedulingConfig、SecurityConfig</t>
+AppTime、BackupProperties、BootstrapAdminInitializer、ClockConfig、DevDataInitializer、SchedulingConfig、SecurityConfig</t>
         </is>
       </c>
     </row>
@@ -2509,12 +2744,12 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>リクエスト／レスポンス record
-AlertBaseRow、ApprovalCommentRequest、ApprovalResultResponse、AttendanceItem、ClockInResponse、ClockOutResponse、CreateRequestRequest、CreateRequestResponse、ErrorResponse、GrantCandidate、HolidayDetailResponse、HolidayListResponse、HolidayRequest、HolidayResponse、LeaveBalanceResponse、LeaveGrantAdjustRequest、LeaveGrantCreateRequest、LeaveGrantListResponse、LeaveGrantResponse、LeaveGrantRow、LeaveTypeDetailResponse、LeaveTypeListResponse、LeaveTypeOptionListResponse、LeaveTypeOptionResponse、LeaveTypeRequest、LeaveTypeResponse、LoginRequest、LoginResponse、MonthlyAttendanceResponse、MonthlyReportResponse、MonthlyReportRow、NotificationListResponse、NotificationResponse、PasswordResetRequest、PendingApprovalItem、PendingApprovalListResponse、PendingApprovalRow、RequestDetail、RequestDetailResponse、RequestListResponse、RequestSummary、StepDetail、SubmitRequestResponse、SubordinateSummaryResponse、UserCreateRequest、UserDetailResponse、UserListResponse、UserResponse、UserUpdateRequest、WithdrawResponse</t>
+AlertBaseRow、ApprovalCommentRequest、ApprovalResultResponse、AttendanceItem、ChangePasswordRequest、ClockInResponse、ClockOutResponse、CreateRequestRequest、CreateRequestResponse、ErrorResponse、GrantCandidate、HolidayDetailResponse、HolidayListResponse、HolidayRequest、HolidayResponse、LeaveBalanceResponse、LeaveGrantAdjustRequest、LeaveGrantCreateRequest、LeaveGrantListResponse、LeaveGrantResponse、LeaveGrantRow、LeaveTypeDetailResponse、LeaveTypeListResponse、LeaveTypeOptionListResponse、LeaveTypeOptionResponse、LeaveTypeRequest、LeaveTypeResponse、LoginRequest、LoginResponse、MonthlyAttendanceResponse、MonthlyReportResponse、MonthlyReportRow、NotificationListResponse、NotificationResponse、PasswordResetRequest、PendingApprovalItem、PendingApprovalListResponse、PendingApprovalRow、RequestDetail、RequestDetailResponse、RequestListResponse、RequestSummary、StepDetail、SubmitRequestResponse、SubordinateSummaryResponse、UserCreateRequest、UserDetailResponse、UserListResponse、UserResponse、UserUpdateRequest、WithdrawResponse</t>
         </is>
       </c>
     </row>
@@ -2573,12 +2808,12 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>JWT 生成（JwtService）、401 / 403 の JSON 応答（RestAuthenticationEntryPoint / RestAccessDeniedHandler）。検証は Spring Security リソースサーバ
-JwtService、RestAccessDeniedHandler、RestAuthenticationEntryPoint</t>
+          <t>JWT 生成（JwtService）。401 / 403 の JSON 応答は SecurityConfig のラムダ（writeError）、検証は Spring Security リソースサーバ
+JwtService</t>
         </is>
       </c>
     </row>
@@ -2973,7 +3208,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ONL-023</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -3283,7 +3518,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="34" customHeight="1">
+    <row r="18" ht="49" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Service</t>
@@ -3296,7 +3531,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>ログイン業務ロジック（ONL-001 本体）</t>
+          <t>ログイン業務ロジック（ONL-001 本体）。ロック判定・失敗回数管理を含む。changePassword / validatePolicy は ONL-023 で追加</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -3306,7 +3541,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ONL-023</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -3851,7 +4086,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>JWT 発行</t>
+          <t>JWT 発行（有効 2 時間）</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -3878,74 +4113,74 @@
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>RestAccessDeniedHandler</t>
+          <t>ApprovalStepRepository</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>フィルタ段階の権限不足を 403 / E-010 の JSON で返す</t>
+          <t>approval_steps の登録・検索</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>ONL-001</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ONL-007、ONL-008、ONL-009、ONL-010、ONL-011、ONL-012、ONL-022</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-01_認証・共通基盤_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-04_承認_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35" ht="34" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>RestAuthenticationEntryPoint</t>
+          <t>AttendanceRecordRepository</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>未認証・トークン不正・期限切れを 401 / E-001 の JSON で返す</t>
+          <t>attendance_records の検索（行ロック付き）・保存</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>ONL-001</t>
+          <t>ONL-002</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ONL-003、ONL-004、ONL-010</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-01_認証・共通基盤_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-02_勤怠打刻_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -3957,32 +4192,32 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>ApprovalStepRepository</t>
+          <t>DepartmentRepository</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>approval_steps の登録・検索</t>
+          <t>部署名の取得（findById）</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>ONL-005</t>
+          <t>ONL-007</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>ONL-007、ONL-008、ONL-009、ONL-010、ONL-011、ONL-012、ONL-022</t>
+          <t>ONL-014</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>07</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-04_承認_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-07_ユーザー・部署管理_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -3994,32 +4229,32 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>AttendanceRecordRepository</t>
+          <t>HolidayRepository</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>attendance_records の検索（行ロック付き）・保存</t>
+          <t>holidays の期間検索・存在確認</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>ONL-002</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>ONL-003、ONL-004、ONL-010</t>
+          <t>ONL-016</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>05</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-02_勤怠打刻_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-05_休暇・休日_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -4031,32 +4266,32 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>DepartmentRepository</t>
+          <t>LeaveBalanceRepository</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>部署名の取得（findById）</t>
+          <t>leave_balances の残日数集計</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>ONL-007</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>ONL-014</t>
+          <t>BAT-001、BAT-002、ONL-013、ONL-017</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>05</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-07_ユーザー・部署管理_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-05_休暇・休日_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -4068,12 +4303,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>HolidayRepository</t>
+          <t>LeaveTypeRepository</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>holidays の期間検索・存在確認</t>
+          <t>leave_types の ID 検索（JpaRepository#findById を使用）</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -4083,7 +4318,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>ONL-016</t>
+          <t>BAT-001、BAT-002、ONL-006、ONL-007、ONL-013、ONL-015、ONL-017、ONL-021</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -4105,12 +4340,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>LeaveBalanceRepository</t>
+          <t>NotificationRepository</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>leave_balances の残日数集計</t>
+          <t>notifications の登録（JpaRepository#save）。検索系は ONL-019 が追加</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -4120,21 +4355,21 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>BAT-001、BAT-002、ONL-013、ONL-017</t>
+          <t>BAT-002、ONL-019</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>06</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-05_休暇・休日_クラス詳細設計書.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="34" customHeight="1">
+          <t>KF-DD-CLS-06_通知_クラス詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="19" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Repository</t>
@@ -4142,180 +4377,180 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>LeaveTypeRepository</t>
+          <t>ReportRepository</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>leave_types の ID 検索（JpaRepository#findById を使用）</t>
+          <t>月次集計の集計 SQL（GROUP BY を 1 本で発行）</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
+          <t>ONL-018</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>ONL-020</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>KF-DD-CLS-08_集計_クラス詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="49" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Repository</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>RequestRepository</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>requests の検索・登録・行ロック</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
           <t>ONL-005</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>BAT-001、BAT-002、ONL-006、ONL-007、ONL-013、ONL-015、ONL-017、ONL-021</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>KF-DD-CLS-05_休暇・休日_クラス詳細設計書.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>BAT-002、ONL-006、ONL-007、ONL-008、ONL-010、ONL-011、ONL-012、ONL-013、ONL-022</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>KF-DD-CLS-03_申請_クラス詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="64" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Repository</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>NotificationRepository</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>notifications の登録（JpaRepository#save）。検索系は ONL-019 が追加</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>UserRepository</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>users のメール検索 findByEmail</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>ONL-001</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>BAT-001、BAT-002、ONL-005、ONL-007、ONL-008、ONL-009、ONL-010、ONL-011、ONL-012、ONL-013、ONL-014、ONL-017、ONL-022、ONL-023</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>KF-DD-CLS-07_ユーザー・部署管理_クラス詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>ApprovalStep</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>approval_steps テーブルのマッピング</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>ONL-005</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>BAT-002、ONL-019</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>KF-DD-CLS-06_通知_クラス詳細設計書.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="19" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Repository</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>ReportRepository</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>月次集計の集計 SQL（GROUP BY を 1 本で発行）</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>ONL-018</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>ONL-020</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>KF-DD-CLS-08_集計_クラス詳細設計書.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="49" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Repository</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>RequestRepository</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>requests の検索・登録・行ロック</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>ONL-005</t>
-        </is>
-      </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>BAT-002、ONL-006、ONL-007、ONL-008、ONL-010、ONL-011、ONL-012、ONL-013、ONL-022</t>
+          <t>ONL-007、ONL-009、ONL-010、ONL-011、ONL-012、ONL-022</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-03_申請_クラス詳細設計書.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="64" customHeight="1">
+          <t>KF-DD-CLS-04_承認_クラス詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="34" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>UserRepository</t>
+          <t>AttendanceRecord</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>users のメール検索</t>
+          <t>attendance_records テーブルのマッピング</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>ONL-001</t>
+          <t>ONL-002</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>BAT-001、BAT-002、ONL-005、ONL-007、ONL-008、ONL-009、ONL-010、ONL-011、ONL-012、ONL-013、ONL-014、ONL-017、ONL-022</t>
+          <t>ONL-003、ONL-004、ONL-010</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>02</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-07_ユーザー・部署管理_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-02_勤怠打刻_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -4327,32 +4562,32 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>ApprovalStep</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>approval_steps テーブルのマッピング</t>
+          <t>departments のマッピング</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>ONL-005</t>
+          <t>ONL-007</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>ONL-007、ONL-009、ONL-010、ONL-011、ONL-012、ONL-022</t>
+          <t>ONL-009、ONL-014</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>07</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-04_承認_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-07_ユーザー・部署管理_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -4364,32 +4599,32 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>AttendanceRecord</t>
+          <t>Holiday</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>attendance_records テーブルのマッピング</t>
+          <t>holidays テーブルのマッピング</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>ONL-002</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>ONL-003、ONL-004、ONL-010</t>
+          <t>ONL-016</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>05</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-02_勤怠打刻_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-05_休暇・休日_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -4401,32 +4636,32 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>LeaveBalance</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>departments のマッピング</t>
+          <t>leave_balances テーブルのマッピング</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>ONL-007</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>ONL-009、ONL-014</t>
+          <t>BAT-001、ONL-013、ONL-017</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>05</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-07_ユーザー・部署管理_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-05_休暇・休日_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -4438,12 +4673,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Holiday</t>
+          <t>LeaveType</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>holidays テーブルのマッピング</t>
+          <t>leave_types テーブルのマッピング</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -4453,7 +4688,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>ONL-016</t>
+          <t>BAT-001、ONL-006、ONL-007、ONL-013、ONL-015、ONL-017、ONL-021</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -4475,12 +4710,12 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>LeaveBalance</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>leave_balances テーブルのマッピング</t>
+          <t>notifications テーブルのマッピング（type / requestId を含む）</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -4490,21 +4725,21 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>BAT-001、ONL-013、ONL-017</t>
+          <t>BAT-001、ONL-019</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>06</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-05_休暇・休日_クラス詳細設計書.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="34" customHeight="1">
+          <t>KF-DD-CLS-06_通知_クラス詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="49" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -4512,12 +4747,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>LeaveType</t>
+          <t>Request</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>leave_types テーブルのマッピング</t>
+          <t>requests テーブルのマッピング</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -4527,21 +4762,21 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>BAT-001、ONL-006、ONL-007、ONL-013、ONL-015、ONL-017、ONL-021</t>
+          <t>ONL-006、ONL-007、ONL-008、ONL-009、ONL-010、ONL-011、ONL-012、ONL-013、ONL-022</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>03</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-05_休暇・休日_クラス詳細設計書.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="34" customHeight="1">
+          <t>KF-DD-CLS-03_申請_クラス詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="64" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -4549,106 +4784,106 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>User</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>notifications テーブルのマッピング（type / requestId を含む）</t>
+          <t>users テーブルのマッピング（failedLoginCount / lockedUntil / mustChangePassword / passwordChangedAt を含む）</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
+          <t>ONL-001</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>BAT-001、ONL-005、ONL-007、ONL-009、ONL-010、ONL-011、ONL-012、ONL-013、ONL-014、ONL-017、ONL-018、ONL-020、ONL-023</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>KF-DD-CLS-07_ユーザー・部署管理_クラス詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>定数</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>LeaveUnit</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>休暇単位コード（FULL / AM / PM）の String 定数（KF-BD-005）</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
           <t>ONL-005</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>BAT-001、ONL-019</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>KF-DD-CLS-03_申請_クラス詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="34" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>定数</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>NotificationType</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>通知種別の String 定数。BAT-001 は LEAVE_GRANTED を使用</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>ONL-005</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>BAT-001、BAT-002</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>06</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>KF-DD-CLS-06_通知_クラス詳細設計書.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="49" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Request</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>requests テーブルのマッピング</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>ONL-005</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>ONL-006、ONL-007、ONL-008、ONL-009、ONL-010、ONL-011、ONL-012、ONL-013、ONL-022</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>KF-DD-CLS-03_申請_クラス詳細設計書.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="49" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>users テーブルのマッピング</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>ONL-001</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>BAT-001、ONL-005、ONL-007、ONL-009、ONL-010、ONL-011、ONL-012、ONL-013、ONL-014、ONL-017、ONL-018、ONL-020</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>KF-DD-CLS-07_ユーザー・部署管理_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -4660,12 +4895,12 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>LeaveUnit</t>
+          <t>RequestStatus</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>休暇単位コード（FULL / AM / PM）の String 定数（KF-BD-005）</t>
+          <t>申請状態コード（DRAFT / PENDING / APPROVED / REJECTED / RETURNED / WITHDRAWN）の String 定数（KF-BD-005）</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -4675,7 +4910,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ONL-006、ONL-008、ONL-010、ONL-022</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -4697,12 +4932,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>NotificationType</t>
+          <t>RequestType</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>通知種別の String 定数。BAT-001 は LEAVE_GRANTED を使用</t>
+          <t>申請種別コード（LEAVE / CLOCK_CORRECTION）の String 定数（KF-BD-005）</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -4712,17 +4947,17 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>BAT-001、BAT-002</t>
+          <t>ONL-010</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>03</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-06_通知_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-03_申請_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -4734,12 +4969,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>RequestStatus</t>
+          <t>StepStatus</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>申請状態コード（DRAFT / PENDING / APPROVED / REJECTED / RETURNED / WITHDRAWN）の String 定数（KF-BD-005）</t>
+          <t>承認ステップ状態コード（WAITING / APPROVED / RETURNED / REJECTED 等）の String 定数（KF-BD-005）</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -4749,7 +4984,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>ONL-006、ONL-008、ONL-010、ONL-022</t>
+          <t>ONL-010</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -4763,114 +4998,114 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="34" customHeight="1">
+    <row r="58" ht="49" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>定数</t>
+          <t>DTO</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>RequestType</t>
+          <t>AlertBaseRow</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>申請種別コード（LEAVE / CLOCK_CORRECTION）の String 定数（KF-BD-005）</t>
+          <t>対象行 (Long userId, String userName, LocalDate grantedOn, BigDecimal grantedDays)。LeaveBalance と氏名から Service が組み立てる（of(LeaveBalance, String)）</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>ONL-005</t>
+          <t>BAT-002</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>ONL-010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>09</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-03_申請_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-09_バッチ_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59" ht="34" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>定数</t>
+          <t>DTO</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>StepStatus</t>
+          <t>ApprovalCommentRequest</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>承認ステップ状態コード（WAITING / APPROVED / RETURNED / REJECTED 等）の String 定数（KF-BD-005）</t>
+          <t>リクエスト（comment）＋入力チェック。ONL-011/012 も共用</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>ONL-005</t>
+          <t>ONL-010</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
+          <t>ONL-011、ONL-012</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>KF-DD-CLS-04_承認_クラス詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="34" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>DTO</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>ApprovalResultResponse</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>承認・差戻し・却下（API-010〜012）の共用応答（requestStatus）</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
           <t>ONL-010</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>KF-DD-CLS-03_申請_クラス詳細設計書.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="49" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>DTO</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>AlertBaseRow</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>対象行 (Long userId, String userName, LocalDate grantedOn, BigDecimal grantedDays)。LeaveBalance と氏名から Service が組み立てる（of(LeaveBalance, String)）</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>BAT-002</t>
-        </is>
-      </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ONL-011、ONL-012</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>04</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-09_バッチ_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-04_承認_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -4882,36 +5117,36 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>ApprovalCommentRequest</t>
+          <t>AttendanceItem</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>リクエスト（comment）＋入力チェック。ONL-011/012 も共用</t>
+          <t>月次勤怠 1 日分（record）。MonthlyAttendanceResponse.records の要素</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>ONL-010</t>
+          <t>ONL-004</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>ONL-011、ONL-012</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>02</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-04_承認_クラス詳細設計書.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="34" customHeight="1">
+          <t>KF-DD-CLS-02_勤怠打刻_クラス詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="49" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
           <t>DTO</t>
@@ -4919,32 +5154,32 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>ApprovalResultResponse</t>
+          <t>BatchResult</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>承認・差戻し・却下（API-010〜012）の共用応答（requestStatus）</t>
+          <t>バッチ実行結果の record（件数・状態）。status() と終了コード（0:正常 1:一部失敗 2:異常）・サマリ文字列の算出。3 バッチ共通</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>ONL-010</t>
+          <t>BAT-001</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>ONL-011、ONL-012</t>
+          <t>BAT-002、BAT-003</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>09</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-04_承認_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-09_バッチ_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -4956,69 +5191,69 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>AttendanceItem</t>
+          <t>BatchStatus</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>月次勤怠 1 日分（record）。MonthlyAttendanceResponse.records の要素</t>
+          <t>バッチ終了状態の enum（SUCCESS(0) / PARTIAL(1) / FAILED(2)）。終了コードとログレベルを決める。3 バッチ共通</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>ONL-004</t>
+          <t>BAT-001</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
+          <t>BAT-002、BAT-003</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>KF-DD-CLS-09_バッチ_クラス詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="34" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>DTO</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>ChangePasswordRequest</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>リクエスト（currentPassword / newPassword）と入力チェック定義</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>ONL-023</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>KF-DD-CLS-02_勤怠打刻_クラス詳細設計書.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="49" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>DTO</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>BatchResult</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>バッチ実行結果の record（件数・状態）。status() と終了コード（0:正常 1:一部失敗 2:異常）・サマリ文字列の算出。3 バッチ共通</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>BAT-001</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>BAT-002、BAT-003</t>
-        </is>
-      </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>01</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-09_バッチ_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-01_認証・共通基盤_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -5030,32 +5265,32 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>BatchStatus</t>
+          <t>ClockInResponse</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>バッチ終了状態の enum（SUCCESS(0) / PARTIAL(1) / FAILED(2)）。終了コードとログレベルを決める。3 バッチ共通</t>
+          <t>出勤打刻の正常応答（workDate, clockIn）</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>BAT-001</t>
+          <t>ONL-002</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>BAT-002、BAT-003</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>02</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-09_バッチ_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-02_勤怠打刻_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -5067,17 +5302,17 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>ClockInResponse</t>
+          <t>ClockOutResponse</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>出勤打刻の正常応答（workDate, clockIn）</t>
+          <t>退勤打刻の正常応答（clockOut, workMinutes, overtimeMinutes）</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>ONL-002</t>
+          <t>ONL-003</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -5096,7 +5331,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="34" customHeight="1">
+    <row r="67" ht="19" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
           <t>DTO</t>
@@ -5104,17 +5339,17 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>ClockOutResponse</t>
+          <t>CreateRequestRequest</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>退勤打刻の正常応答（clockOut, workMinutes, overtimeMinutes）</t>
+          <t>リクエスト＋入力チェック定義</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>ONL-003</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -5124,12 +5359,12 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-02_勤怠打刻_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-03_申請_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -5141,12 +5376,12 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CreateRequestRequest</t>
+          <t>CreateRequestResponse</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>リクエスト＋入力チェック定義</t>
+          <t>正常応答 {requestId, status}</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -5170,7 +5405,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="19" customHeight="1">
+    <row r="69" ht="34" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
           <t>DTO</t>
@@ -5178,32 +5413,32 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>CreateRequestResponse</t>
+          <t>ErrorResponse</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>正常応答 {requestId, status}</t>
+          <t>共通エラー応答 {code, message, fieldErrors[]}（record）</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>ONL-005</t>
+          <t>ONL-001</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ONL-002、ONL-005、ONL-006、ONL-007、ONL-008、ONL-019、ONL-021、ONL-022</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-03_申請_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-01_認証・共通基盤_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -5215,32 +5450,32 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>ErrorResponse</t>
+          <t>GrantCandidate</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>共通エラー応答 {code, message, fieldErrors[]}（record）</t>
+          <t>候補抽出の戻り型 (Long id, LocalDate hireDate)。氏名・メールは取得しない</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>ONL-001</t>
+          <t>BAT-001</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>ONL-002、ONL-005、ONL-006、ONL-007、ONL-008、ONL-019、ONL-021、ONL-022</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>09</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-01_認証・共通基盤_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-09_バッチ_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -5252,17 +5487,17 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>GrantCandidate</t>
+          <t>HolidayDetailResponse</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>候補抽出の戻り型 (Long id, LocalDate hireDate)。氏名・メールは取得しない</t>
+          <t>単一応答 {holiday}（登録・削除）</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>BAT-001</t>
+          <t>ONL-016</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -5272,12 +5507,12 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>05</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-09_バッチ_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-05_休暇・休日_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -5289,12 +5524,12 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>HolidayDetailResponse</t>
+          <t>HolidayListResponse</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>単一応答 {holiday}（登録・削除）</t>
+          <t>一覧応答 {year, holidays[]}</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -5326,12 +5561,12 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>HolidayListResponse</t>
+          <t>HolidayRequest</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>一覧応答 {year, holidays[]}</t>
+          <t>登録リクエスト＋入力チェック</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -5363,12 +5598,12 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>HolidayRequest</t>
+          <t>HolidayResponse</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>登録リクエスト＋入力チェック</t>
+          <t>祝日1件の表現</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -5400,17 +5635,17 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>HolidayResponse</t>
+          <t>LeaveBalanceResponse</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>祝日1件の表現</t>
+          <t>正常応答。入れ子 record: Item（種別ごと）/ Grant（付与行ごと）/ Mandatory5（年5日進捗）</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>ONL-016</t>
+          <t>ONL-013</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -5437,17 +5672,17 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>LeaveBalanceResponse</t>
+          <t>LeaveGrantAdjustRequest</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>正常応答。入れ子 record: Item（種別ごと）/ Grant（付与行ごと）/ Mandatory5（年5日進捗）</t>
+          <t>PUT リクエスト＋入力チェック定義</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>ONL-013</t>
+          <t>ONL-017</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -5474,12 +5709,12 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>LeaveGrantAdjustRequest</t>
+          <t>LeaveGrantCreateRequest</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>PUT リクエスト＋入力チェック定義</t>
+          <t>POST リクエスト＋入力チェック定義</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -5511,12 +5746,12 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>LeaveGrantCreateRequest</t>
+          <t>LeaveGrantListResponse</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>POST リクエスト＋入力チェック定義</t>
+          <t>GET 応答（従業員情報＋ grants[]）</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -5548,12 +5783,12 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>LeaveGrantListResponse</t>
+          <t>LeaveGrantResponse</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>GET 応答（従業員情報＋ grants[]）</t>
+          <t>付与 1 行分の応答（POST/PUT の戻り・GET の要素）</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -5585,12 +5820,12 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>LeaveGrantResponse</t>
+          <t>LeaveGrantRow</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>付与 1 行分の応答（POST/PUT の戻り・GET の要素）</t>
+          <t>findGrantRows の戻り型（内部用）</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -5622,17 +5857,17 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>LeaveGrantRow</t>
+          <t>LeaveTypeDetailResponse</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>findGrantRows の戻り型（内部用）</t>
+          <t>単一応答 {leaveType}</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>ONL-017</t>
+          <t>ONL-015</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -5659,12 +5894,12 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>LeaveTypeDetailResponse</t>
+          <t>LeaveTypeListResponse</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>単一応答 {leaveType}</t>
+          <t>一覧応答 {leaveTypes[]}</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -5696,7 +5931,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>LeaveTypeListResponse</t>
+          <t>LeaveTypeOptionListResponse</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -5706,7 +5941,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>ONL-015</t>
+          <t>ONL-021</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -5733,12 +5968,12 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>LeaveTypeOptionListResponse</t>
+          <t>LeaveTypeOptionResponse</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>一覧応答 {leaveTypes[]}</t>
+          <t>プルダウン用 1 件（5 項目）。ONL-015 の LeaveTypeResponse（管理者用 7 項目）とは別</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -5770,17 +6005,17 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>LeaveTypeOptionResponse</t>
+          <t>LeaveTypeRequest</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>プルダウン用 1 件（5 項目）。ONL-015 の LeaveTypeResponse（管理者用 7 項目）とは別</t>
+          <t>登録・変更リクエスト＋入力チェック</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>ONL-021</t>
+          <t>ONL-015</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -5807,12 +6042,12 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>LeaveTypeRequest</t>
+          <t>LeaveTypeResponse</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>登録・変更リクエスト＋入力チェック</t>
+          <t>休暇種別1件の表現</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -5844,17 +6079,17 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>LeaveTypeResponse</t>
+          <t>LoginRequest</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>休暇種別1件の表現</t>
+          <t>リクエスト＋入力チェック定義</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>ONL-015</t>
+          <t>ONL-001</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -5864,12 +6099,12 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>01</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-05_休暇・休日_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-01_認証・共通基盤_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -5881,12 +6116,12 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>LoginRequest</t>
+          <t>LoginResponse</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>リクエスト＋入力チェック定義</t>
+          <t>正常応答（token / userId / name / role / mustChangePassword）</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -5918,17 +6153,17 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>LoginResponse</t>
+          <t>MonthlyAttendanceResponse</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>正常応答</t>
+          <t>正常応答（records[], totalWorkMinutes, totalOvertimeMinutes）</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>ONL-001</t>
+          <t>ONL-004</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -5938,16 +6173,16 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-01_認証・共通基盤_クラス詳細設計書.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="34" customHeight="1">
+          <t>KF-DD-CLS-02_勤怠打刻_クラス詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="19" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
           <t>DTO</t>
@@ -5955,17 +6190,17 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>MonthlyAttendanceResponse</t>
+          <t>MonthlyReportResponse</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>正常応答（records[], totalWorkMinutes, totalOvertimeMinutes）</t>
+          <t>JSON 応答（month / departmentId / rows[]）</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>ONL-004</t>
+          <t>ONL-018</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -5975,12 +6210,12 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>08</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-02_勤怠打刻_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-08_集計_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -5992,12 +6227,12 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>MonthlyReportResponse</t>
+          <t>MonthlyReportRow</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>JSON 応答（month / departmentId / rows[]）</t>
+          <t>社員 1 行分の集計（ONL-020 と共用）</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -6007,7 +6242,7 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ONL-020</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -6029,36 +6264,36 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>MonthlyReportRow</t>
+          <t>NotificationListResponse</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>社員 1 行分の集計（ONL-020 と共用）</t>
+          <t>GET の正常応答（notifications[]）</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>ONL-018</t>
+          <t>ONL-019</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>ONL-020</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>06</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-08_集計_クラス詳細設計書.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="19" customHeight="1">
+          <t>KF-DD-CLS-06_通知_クラス詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="34" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
           <t>DTO</t>
@@ -6066,12 +6301,12 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>NotificationListResponse</t>
+          <t>NotificationResponse</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>GET の正常応答（notifications[]）</t>
+          <t>通知1件（id, type, message, requestId, createdAt, isRead）。POST の応答にも使用</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -6103,17 +6338,17 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>NotificationResponse</t>
+          <t>PasswordResetRequest</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>通知1件（id, type, message, requestId, createdAt, isRead）。POST の応答にも使用</t>
+          <t>パスワード設定リクエスト＋入力チェック</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>ONL-019</t>
+          <t>ONL-014</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
@@ -6123,16 +6358,16 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-06_通知_クラス詳細設計書.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="34" customHeight="1">
+          <t>KF-DD-CLS-07_ユーザー・部署管理_クラス詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="19" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
           <t>DTO</t>
@@ -6140,17 +6375,17 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>PasswordResetRequest</t>
+          <t>PendingApprovalItem</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>パスワード設定リクエスト＋入力チェック</t>
+          <t>応答の1行（日時は +09:00 付き ISO 8601 文字列）</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>ONL-014</t>
+          <t>ONL-009</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -6160,12 +6395,12 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>04</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-07_ユーザー・部署管理_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-04_承認_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -6177,12 +6412,12 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>PendingApprovalItem</t>
+          <t>PendingApprovalListResponse</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>応答の1行（日時は +09:00 付き ISO 8601 文字列）</t>
+          <t>正常応答（items）</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -6206,7 +6441,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="19" customHeight="1">
+    <row r="97" ht="34" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
           <t>DTO</t>
@@ -6214,12 +6449,12 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>PendingApprovalListResponse</t>
+          <t>PendingApprovalRow</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>正常応答（items）</t>
+          <t>検索結果の1行（LocalDateTime のまま。JPQL コンストラクタ式用）</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -6251,17 +6486,17 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>PendingApprovalRow</t>
+          <t>RequestDetail</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>検索結果の1行（LocalDateTime のまま。JPQL コンストラクタ式用）</t>
+          <t>RequestDetailResponse に入れ子となる申請内容（record）</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>ONL-009</t>
+          <t>ONL-007</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
@@ -6271,12 +6506,12 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-04_承認_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-03_申請_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -6288,12 +6523,12 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>RequestDetail</t>
+          <t>RequestDetailResponse</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>RequestDetailResponse に入れ子となる申請内容（record）</t>
+          <t>申請詳細（API-007）の正常応答。申請内容・承認履歴・申請者残日数を持つ</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -6317,7 +6552,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="34" customHeight="1">
+    <row r="100" ht="19" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
           <t>DTO</t>
@@ -6325,17 +6560,17 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>RequestDetailResponse</t>
+          <t>RequestListResponse</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>申請詳細（API-007）の正常応答。申請内容・承認履歴・申請者残日数を持つ</t>
+          <t>正常応答 {requests: [...]}</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>ONL-007</t>
+          <t>ONL-006</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -6362,12 +6597,12 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>RequestListResponse</t>
+          <t>RequestSummary</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>正常応答 {requests: [...]}</t>
+          <t>一覧の1行分</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -6391,7 +6626,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="19" customHeight="1">
+    <row r="102" ht="34" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
           <t>DTO</t>
@@ -6399,17 +6634,17 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>RequestSummary</t>
+          <t>StepDetail</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>一覧の1行分</t>
+          <t>RequestDetailResponse に入れ子となる承認履歴 1 ステップ分（record）</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>ONL-006</t>
+          <t>ONL-007</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -6428,7 +6663,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="34" customHeight="1">
+    <row r="103" ht="19" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
           <t>DTO</t>
@@ -6436,17 +6671,17 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>StepDetail</t>
+          <t>SubmitRequestResponse</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>RequestDetailResponse に入れ子となる承認履歴 1 ステップ分（record）</t>
+          <t>正常応答 {requestId, status}</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>ONL-007</t>
+          <t>ONL-022</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -6473,17 +6708,17 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>SubmitRequestResponse</t>
+          <t>SubordinateSummaryResponse</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>正常応答 {requestId, status}</t>
+          <t>応答（month / rows[]）</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>ONL-022</t>
+          <t>ONL-020</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -6493,16 +6728,16 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>08</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-03_申請_クラス詳細設計書.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="19" customHeight="1">
+          <t>KF-DD-CLS-08_集計_クラス詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="34" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
           <t>DTO</t>
@@ -6510,17 +6745,17 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>SubordinateSummaryResponse</t>
+          <t>UserCreateRequest</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>応答（month / rows[]）</t>
+          <t>登録リクエスト＋入力チェック</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>ONL-020</t>
+          <t>ONL-014</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -6530,12 +6765,12 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-08_集計_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-07_ユーザー・部署管理_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -6547,12 +6782,12 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>UserCreateRequest</t>
+          <t>UserDetailResponse</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>登録リクエスト＋入力チェック</t>
+          <t>単一応答 {user}</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -6584,12 +6819,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>UserDetailResponse</t>
+          <t>UserListResponse</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>単一応答 {user}</t>
+          <t>一覧応答 {users[], total}</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -6621,12 +6856,12 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>UserListResponse</t>
+          <t>UserResponse</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>一覧応答 {users[], total}</t>
+          <t>ユーザー1件の表現（password_hash は含めない）</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -6658,12 +6893,12 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>UserResponse</t>
+          <t>UserUpdateRequest</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>ユーザー1件の表現（password_hash は含めない）</t>
+          <t>変更・無効化リクエスト＋入力チェック</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -6687,7 +6922,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="34" customHeight="1">
+    <row r="110" ht="19" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
           <t>DTO</t>
@@ -6695,17 +6930,17 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>UserUpdateRequest</t>
+          <t>WithdrawResponse</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>変更・無効化リクエスト＋入力チェック</t>
+          <t>正常応答 {status}</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>ONL-014</t>
+          <t>ONL-008</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -6715,34 +6950,34 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>03</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-07_ユーザー・部署管理_クラス詳細設計書.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="19" customHeight="1">
+          <t>KF-DD-CLS-03_申請_クラス詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="49" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>DTO</t>
+          <t>Config</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>WithdrawResponse</t>
+          <t>BackupProperties</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>正常応答 {status}</t>
+          <t>kintaiflow.batch.backup.* の設定値（DB 接続・保存先・世代数・pg_dump パス・タイムアウト）。toString でパスワードを出さない</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>ONL-008</t>
+          <t>BAT-003</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -6752,16 +6987,16 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>09</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-03_申請_クラス詳細設計書.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="49" customHeight="1">
+          <t>KF-DD-CLS-09_バッチ_クラス詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="34" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
           <t>Config</t>
@@ -6769,32 +7004,32 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>BackupProperties</t>
+          <t>BootstrapAdminInitializer</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>kintaiflow.batch.backup.* の設定値（DB 接続・保存先・世代数・pg_dump パス・タイムアウト）。toString でパスワードを出さない</t>
+          <t>初期管理者（ADMIN）1 名の作成（@Order(2)。users が空かつ bootstrap 設定が揃っているときのみ）</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>BAT-003</t>
+          <t>ONL-001</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ONL-023</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>01</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-CLS-09_バッチ_クラス詳細設計書.xlsx</t>
+          <t>KF-DD-CLS-01_認証・共通基盤_クラス詳細設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -6848,7 +7083,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>開発用テストユーザー投入（本番では無効）</t>
+          <t>開発用テストユーザー 100 名の投入（@Order(1)。seed-password 設定時のみ）</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -6909,7 +7144,7 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="34" customHeight="1">
+    <row r="116" ht="49" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
           <t>Config</t>
@@ -6922,7 +7157,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>認証・認可・BCrypt・JWT・CORS の Bean 定義</t>
+          <t>認証・認可・BCrypt・JWT・CORS の Bean 定義。401 / 403 の JSON 応答（writeError）を含む</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -6932,7 +7167,7 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>ONL-002、ONL-009、ONL-014、ONL-015、ONL-016、ONL-017、ONL-018、ONL-020</t>
+          <t>ONL-002、ONL-009、ONL-014、ONL-015、ONL-016、ONL-017、ONL-018、ONL-020、ONL-023</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
@@ -7006,7 +7241,7 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>ONL-002、ONL-003、ONL-004、ONL-005、ONL-006、ONL-007、ONL-008、ONL-009、ONL-010、ONL-011、ONL-012、ONL-013、ONL-014、ONL-015、ONL-016、ONL-017、ONL-018、ONL-019、ONL-020、ONL-022</t>
+          <t>ONL-002、ONL-003、ONL-004、ONL-005、ONL-006、ONL-007、ONL-008、ONL-009、ONL-010、ONL-011、ONL-012、ONL-013、ONL-014、ONL-015、ONL-016、ONL-017、ONL-018、ONL-019、ONL-020、ONL-022、ONL-023</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
@@ -7043,7 +7278,7 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>ONL-002、ONL-003、ONL-004、ONL-005、ONL-006、ONL-007、ONL-008、ONL-009、ONL-010、ONL-011、ONL-012、ONL-014、ONL-015、ONL-016、ONL-017、ONL-018、ONL-019、ONL-020、ONL-021、ONL-022</t>
+          <t>ONL-002、ONL-003、ONL-004、ONL-005、ONL-006、ONL-007、ONL-008、ONL-009、ONL-010、ONL-011、ONL-012、ONL-014、ONL-015、ONL-016、ONL-017、ONL-018、ONL-019、ONL-020、ONL-021、ONL-022、ONL-023</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
@@ -7094,7 +7329,7 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="34" customHeight="1">
+    <row r="121" ht="64" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
           <t>Util</t>
@@ -7107,7 +7342,7 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>メールアドレスの正規化 normalize（trim＋小文字化）。保存時・検索時に共通利用（ONL-014 も使用）</t>
+          <t>【未実装・設計案】メールアドレスの正規化 normalize（trim＋小文字化）。現行コードは AuthService#login 内で trim().toLowerCase(Locale.ROOT) を直接実行しており、ONL-014（ユーザー管理）の実装時に共通化する予定</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -7443,7 +7678,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>AuthController、AuthService、JwtService、RestAccessDeniedHandler、RestAuthenticationEntryPoint、DevDataInitializer、SecurityConfig、ClockConfig、BusinessException、GlobalExceptionHandler、EmailNormalizer、AppTi…</t>
+          <t>AuthController、AuthService、JwtService、BootstrapAdminInitializer、DevDataInitializer、SecurityConfig、ClockConfig、BusinessException、GlobalExceptionHandler、EmailNormalizer、AppTime</t>
         </is>
       </c>
     </row>
@@ -7765,7 +8000,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
       <c r="I4" s="4" t="inlineStr"/>
@@ -7790,7 +8025,7 @@
         <v>30</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>14</v>
@@ -7895,12 +8130,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr"/>
@@ -7956,7 +8195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR71"/>
+  <dimension ref="A1:BQ70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -8028,7 +8267,6 @@
     <col width="3.2" customWidth="1" min="67" max="67"/>
     <col width="3.2" customWidth="1" min="68" max="68"/>
     <col width="3.2" customWidth="1" min="69" max="69"/>
-    <col width="3.2" customWidth="1" min="70" max="70"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8201,185 +8439,180 @@
       </c>
       <c r="AH2" s="12" t="inlineStr">
         <is>
-          <t>RestAccessDeniedHandler</t>
+          <t>ApprovalStepRepository</t>
         </is>
       </c>
       <c r="AI2" s="12" t="inlineStr">
         <is>
-          <t>RestAuthenticationEntryPoint</t>
+          <t>AttendanceRecordRepository</t>
         </is>
       </c>
       <c r="AJ2" s="12" t="inlineStr">
         <is>
-          <t>ApprovalStepRepository</t>
+          <t>DepartmentRepository</t>
         </is>
       </c>
       <c r="AK2" s="12" t="inlineStr">
         <is>
-          <t>AttendanceRecordRepository</t>
+          <t>HolidayRepository</t>
         </is>
       </c>
       <c r="AL2" s="12" t="inlineStr">
         <is>
-          <t>DepartmentRepository</t>
+          <t>LeaveBalanceRepository</t>
         </is>
       </c>
       <c r="AM2" s="12" t="inlineStr">
         <is>
-          <t>HolidayRepository</t>
+          <t>LeaveTypeRepository</t>
         </is>
       </c>
       <c r="AN2" s="12" t="inlineStr">
         <is>
-          <t>LeaveBalanceRepository</t>
+          <t>NotificationRepository</t>
         </is>
       </c>
       <c r="AO2" s="12" t="inlineStr">
         <is>
-          <t>LeaveTypeRepository</t>
+          <t>ReportRepository</t>
         </is>
       </c>
       <c r="AP2" s="12" t="inlineStr">
         <is>
-          <t>NotificationRepository</t>
+          <t>RequestRepository</t>
         </is>
       </c>
       <c r="AQ2" s="12" t="inlineStr">
         <is>
-          <t>ReportRepository</t>
+          <t>UserRepository</t>
         </is>
       </c>
       <c r="AR2" s="12" t="inlineStr">
         <is>
-          <t>RequestRepository</t>
+          <t>ApprovalStep</t>
         </is>
       </c>
       <c r="AS2" s="12" t="inlineStr">
         <is>
-          <t>UserRepository</t>
+          <t>AttendanceRecord</t>
         </is>
       </c>
       <c r="AT2" s="12" t="inlineStr">
         <is>
-          <t>ApprovalStep</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="AU2" s="12" t="inlineStr">
         <is>
-          <t>AttendanceRecord</t>
+          <t>Holiday</t>
         </is>
       </c>
       <c r="AV2" s="12" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>LeaveBalance</t>
         </is>
       </c>
       <c r="AW2" s="12" t="inlineStr">
         <is>
-          <t>Holiday</t>
+          <t>LeaveType</t>
         </is>
       </c>
       <c r="AX2" s="12" t="inlineStr">
         <is>
-          <t>LeaveBalance</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="AY2" s="12" t="inlineStr">
         <is>
-          <t>LeaveType</t>
+          <t>Request</t>
         </is>
       </c>
       <c r="AZ2" s="12" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>User</t>
         </is>
       </c>
       <c r="BA2" s="12" t="inlineStr">
         <is>
-          <t>Request</t>
+          <t>BackupProperties</t>
         </is>
       </c>
       <c r="BB2" s="12" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>BootstrapAdminInitializer</t>
         </is>
       </c>
       <c r="BC2" s="12" t="inlineStr">
         <is>
-          <t>BackupProperties</t>
+          <t>ClockConfig</t>
         </is>
       </c>
       <c r="BD2" s="12" t="inlineStr">
         <is>
-          <t>ClockConfig</t>
+          <t>DevDataInitializer</t>
         </is>
       </c>
       <c r="BE2" s="12" t="inlineStr">
         <is>
-          <t>DevDataInitializer</t>
+          <t>SchedulingConfig</t>
         </is>
       </c>
       <c r="BF2" s="12" t="inlineStr">
         <is>
-          <t>SchedulingConfig</t>
+          <t>SecurityConfig</t>
         </is>
       </c>
       <c r="BG2" s="12" t="inlineStr">
         <is>
-          <t>SecurityConfig</t>
+          <t>BackupException</t>
         </is>
       </c>
       <c r="BH2" s="12" t="inlineStr">
         <is>
-          <t>BackupException</t>
+          <t>BusinessException</t>
         </is>
       </c>
       <c r="BI2" s="12" t="inlineStr">
         <is>
-          <t>BusinessException</t>
+          <t>GlobalExceptionHandler</t>
         </is>
       </c>
       <c r="BJ2" s="12" t="inlineStr">
         <is>
-          <t>GlobalExceptionHandler</t>
+          <t>AppTime</t>
         </is>
       </c>
       <c r="BK2" s="12" t="inlineStr">
         <is>
-          <t>AppTime</t>
+          <t>EmailNormalizer</t>
         </is>
       </c>
       <c r="BL2" s="12" t="inlineStr">
         <is>
-          <t>EmailNormalizer</t>
+          <t>LeaveGrantCalculator</t>
         </is>
       </c>
       <c r="BM2" s="12" t="inlineStr">
         <is>
-          <t>LeaveGrantCalculator</t>
+          <t>MandatoryLeaveMessages</t>
         </is>
       </c>
       <c r="BN2" s="12" t="inlineStr">
         <is>
-          <t>MandatoryLeaveMessages</t>
+          <t>BackupBatch</t>
         </is>
       </c>
       <c r="BO2" s="12" t="inlineStr">
         <is>
-          <t>BackupBatch</t>
+          <t>BatchRunOnceRunner</t>
         </is>
       </c>
       <c r="BP2" s="12" t="inlineStr">
         <is>
-          <t>BatchRunOnceRunner</t>
+          <t>LeaveGrantBatch</t>
         </is>
       </c>
       <c r="BQ2" s="12" t="inlineStr">
-        <is>
-          <t>LeaveGrantBatch</t>
-        </is>
-      </c>
-      <c r="BR2" s="12" t="inlineStr">
         <is>
           <t>MandatoryLeaveAlertBatch</t>
         </is>
@@ -8456,7 +8689,7 @@
           <t>○</t>
         </is>
       </c>
-      <c r="BA8" s="14" t="inlineStr">
+      <c r="AY8" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -8552,27 +8785,27 @@
           <t>ApprovalRouteService</t>
         </is>
       </c>
-      <c r="AJ16" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AS16" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AT16" s="14" t="inlineStr">
+      <c r="AH16" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AQ16" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AR16" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BA16" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="BB16" s="14" t="inlineStr">
+      <c r="AY16" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AZ16" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -8604,57 +8837,57 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AJ17" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AK17" s="14" t="inlineStr">
+      <c r="AH17" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AI17" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AP17" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AQ17" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
       <c r="AR17" s="14" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>△</t>
         </is>
       </c>
       <c r="AS17" s="14" t="inlineStr">
         <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AT17" s="14" t="inlineStr">
-        <is>
           <t>△</t>
         </is>
       </c>
-      <c r="AU17" s="14" t="inlineStr">
+      <c r="AY17" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BA17" s="14" t="inlineStr">
+      <c r="AZ17" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BB17" s="14" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="BD17" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="BI17" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="BK17" s="14" t="inlineStr">
+      <c r="BC17" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="BH17" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="BJ17" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -8671,22 +8904,22 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AK18" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AU18" s="14" t="inlineStr">
+      <c r="AI18" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AS18" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BI18" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="BK18" s="14" t="inlineStr">
+      <c r="BH18" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="BJ18" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -8703,27 +8936,22 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AS19" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="BA19" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="BB19" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="BI19" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="BL19" s="14" t="inlineStr">
+      <c r="AQ19" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AY19" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AZ19" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="BH19" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -8740,12 +8968,12 @@
           <t>○</t>
         </is>
       </c>
-      <c r="BC20" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="BH20" s="14" t="inlineStr">
+      <c r="BA20" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="BG20" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -8757,17 +8985,17 @@
           <t>HolidayService</t>
         </is>
       </c>
-      <c r="AM21" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AW21" s="14" t="inlineStr">
+      <c r="AK21" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AU21" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BI21" s="14" t="inlineStr">
+      <c r="BH21" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -8784,47 +9012,47 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AN22" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AO22" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AR22" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AS22" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AX22" s="14" t="inlineStr">
+      <c r="AL22" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AM22" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AP22" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AQ22" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AV22" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="AY22" s="14" t="inlineStr">
+      <c r="AW22" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BB22" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="BD22" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="BI22" s="14" t="inlineStr">
+      <c r="AZ22" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="BC22" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="BH22" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -8841,27 +9069,27 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AN23" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AO23" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AS23" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AY23" s="14" t="inlineStr">
+      <c r="AL23" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AM23" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AQ23" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AW23" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BM23" s="14" t="inlineStr">
+      <c r="BL23" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -8883,27 +9111,27 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AN24" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AS24" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AX24" s="14" t="inlineStr">
+      <c r="AL24" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AQ24" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AV24" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BB24" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="BM24" s="14" t="inlineStr">
+      <c r="AZ24" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="BL24" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -8915,17 +9143,17 @@
           <t>LeaveTypeService</t>
         </is>
       </c>
-      <c r="AO25" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AY25" s="14" t="inlineStr">
+      <c r="AM25" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AW25" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BI25" s="14" t="inlineStr">
+      <c r="BH25" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -8947,37 +9175,37 @@
           <t>○</t>
         </is>
       </c>
-      <c r="AO26" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AR26" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AS26" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AX26" s="14" t="inlineStr">
+      <c r="AM26" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AP26" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AQ26" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AV26" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="AY26" s="14" t="inlineStr">
+      <c r="AW26" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BB26" s="14" t="inlineStr">
+      <c r="AZ26" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BN26" s="14" t="inlineStr">
+      <c r="BM26" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -8994,12 +9222,12 @@
           <t>○</t>
         </is>
       </c>
-      <c r="BB27" s="14" t="inlineStr">
+      <c r="AZ27" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BN27" s="14" t="inlineStr">
+      <c r="BM27" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -9011,22 +9239,22 @@
           <t>NotificationService</t>
         </is>
       </c>
-      <c r="AP28" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AZ28" s="14" t="inlineStr">
+      <c r="AN28" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AX28" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BI28" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="BK28" s="14" t="inlineStr">
+      <c r="BH28" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="BJ28" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -9038,12 +9266,12 @@
           <t>ReportService</t>
         </is>
       </c>
-      <c r="AQ29" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="BI29" s="14" t="inlineStr">
+      <c r="AO29" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="BH29" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -9075,29 +9303,34 @@
           <t>○</t>
         </is>
       </c>
+      <c r="AH30" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="AJ30" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="AL30" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AO30" s="14" t="inlineStr">
+      <c r="AM30" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AP30" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AQ30" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
       <c r="AR30" s="14" t="inlineStr">
         <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AS30" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
+          <t>△</t>
         </is>
       </c>
       <c r="AT30" s="14" t="inlineStr">
@@ -9105,32 +9338,27 @@
           <t>△</t>
         </is>
       </c>
-      <c r="AV30" s="14" t="inlineStr">
+      <c r="AW30" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AY30" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="AY30" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="BA30" s="14" t="inlineStr">
+      <c r="AZ30" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BB30" s="14" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="BI30" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="BK30" s="14" t="inlineStr">
+      <c r="BH30" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="BJ30" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -9142,32 +9370,32 @@
           <t>UserService</t>
         </is>
       </c>
-      <c r="AL31" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AS31" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AV31" s="14" t="inlineStr">
+      <c r="AJ31" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AQ31" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AT31" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BB31" s="14" t="inlineStr">
+      <c r="AZ31" s="14" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BI31" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="BL31" s="14" t="inlineStr">
+      <c r="BH31" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="BK31" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -9186,7 +9414,7 @@
           <t>PgDumpRunner</t>
         </is>
       </c>
-      <c r="BH33" s="14" t="inlineStr">
+      <c r="BG33" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -9198,12 +9426,12 @@
           <t>JwtService</t>
         </is>
       </c>
-      <c r="BB34" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="BG34" s="14" t="inlineStr">
+      <c r="AZ34" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="BF34" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -9212,164 +9440,174 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>RestAccessDeniedHandler</t>
+          <t>ApprovalStepRepository</t>
+        </is>
+      </c>
+      <c r="O35" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AR35" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AT35" s="14" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="AU35" s="14" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="AV35" s="14" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="AY35" s="14" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="AZ35" s="14" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>RestAuthenticationEntryPoint</t>
+          <t>AttendanceRecordRepository</t>
+        </is>
+      </c>
+      <c r="AS36" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>ApprovalStepRepository</t>
-        </is>
-      </c>
-      <c r="O37" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
+          <t>DepartmentRepository</t>
         </is>
       </c>
       <c r="AT37" s="14" t="inlineStr">
         <is>
           <t>○</t>
-        </is>
-      </c>
-      <c r="AV37" s="14" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="AW37" s="14" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="AX37" s="14" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="BA37" s="14" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="BB37" s="14" t="inlineStr">
-        <is>
-          <t>△</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>AttendanceRecordRepository</t>
+          <t>HolidayRepository</t>
+        </is>
+      </c>
+      <c r="O38" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AR38" s="14" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="AU38" s="14" t="inlineStr">
         <is>
           <t>○</t>
+        </is>
+      </c>
+      <c r="AV38" s="14" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>DepartmentRepository</t>
+          <t>LeaveBalanceRepository</t>
+        </is>
+      </c>
+      <c r="O39" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U39" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AM39" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AR39" s="14" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="AU39" s="14" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="AV39" s="14" t="inlineStr">
         <is>
           <t>○</t>
+        </is>
+      </c>
+      <c r="AW39" s="14" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="AZ39" s="14" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>HolidayRepository</t>
-        </is>
-      </c>
-      <c r="O40" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AT40" s="14" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>LeaveTypeRepository</t>
         </is>
       </c>
       <c r="AW40" s="14" t="inlineStr">
         <is>
           <t>○</t>
-        </is>
-      </c>
-      <c r="AX40" s="14" t="inlineStr">
-        <is>
-          <t>△</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>LeaveBalanceRepository</t>
-        </is>
-      </c>
-      <c r="O41" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U41" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AO41" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AT41" s="14" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="AW41" s="14" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>NotificationRepository</t>
         </is>
       </c>
       <c r="AX41" s="14" t="inlineStr">
         <is>
           <t>○</t>
-        </is>
-      </c>
-      <c r="AY41" s="14" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="BB41" s="14" t="inlineStr">
-        <is>
-          <t>△</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>LeaveTypeRepository</t>
-        </is>
-      </c>
-      <c r="AY42" s="14" t="inlineStr">
+          <t>ReportRepository</t>
+        </is>
+      </c>
+      <c r="AZ42" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -9378,10 +9616,10 @@
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>NotificationRepository</t>
-        </is>
-      </c>
-      <c r="AZ43" s="14" t="inlineStr">
+          <t>RequestRepository</t>
+        </is>
+      </c>
+      <c r="AY43" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -9390,10 +9628,10 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>ReportRepository</t>
-        </is>
-      </c>
-      <c r="BB44" s="14" t="inlineStr">
+          <t>UserRepository</t>
+        </is>
+      </c>
+      <c r="AZ44" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -9402,104 +9640,114 @@
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>RequestRepository</t>
-        </is>
-      </c>
-      <c r="BA45" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
+          <t>ApprovalStep</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>UserRepository</t>
-        </is>
-      </c>
-      <c r="BB46" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
+          <t>AttendanceRecord</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>ApprovalStep</t>
+          <t>Department</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>AttendanceRecord</t>
+          <t>Holiday</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>LeaveBalance</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>Holiday</t>
+          <t>LeaveType</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>LeaveBalance</t>
+          <t>Notification</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>LeaveType</t>
+          <t>Request</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>User</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>Request</t>
+          <t>BackupProperties</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>BootstrapAdminInitializer</t>
+        </is>
+      </c>
+      <c r="R55" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AQ55" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AZ55" s="14" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>BackupProperties</t>
+          <t>ClockConfig</t>
+        </is>
+      </c>
+      <c r="BJ56" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>ClockConfig</t>
-        </is>
-      </c>
-      <c r="BK57" s="14" t="inlineStr">
+          <t>DevDataInitializer</t>
+        </is>
+      </c>
+      <c r="AQ57" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -9508,71 +9756,71 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>DevDataInitializer</t>
-        </is>
-      </c>
-      <c r="AS58" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
+          <t>SchedulingConfig</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>SchedulingConfig</t>
+          <t>SecurityConfig</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>SecurityConfig</t>
+          <t>BackupException</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>BackupException</t>
+          <t>BusinessException</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>BusinessException</t>
+          <t>GlobalExceptionHandler</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>GlobalExceptionHandler</t>
+          <t>AppTime</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>AppTime</t>
+          <t>EmailNormalizer</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>EmailNormalizer</t>
+          <t>LeaveGrantCalculator</t>
+        </is>
+      </c>
+      <c r="U65" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>LeaveGrantCalculator</t>
-        </is>
-      </c>
-      <c r="U66" s="14" t="inlineStr">
+          <t>MandatoryLeaveMessages</t>
+        </is>
+      </c>
+      <c r="AA66" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -9581,10 +9829,10 @@
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>MandatoryLeaveMessages</t>
-        </is>
-      </c>
-      <c r="AA67" s="14" t="inlineStr">
+          <t>BackupBatch</t>
+        </is>
+      </c>
+      <c r="S67" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -9593,10 +9841,20 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>BackupBatch</t>
+          <t>BatchRunOnceRunner</t>
         </is>
       </c>
       <c r="S68" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="V68" s="14" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Y68" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -9605,12 +9863,7 @@
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>BatchRunOnceRunner</t>
-        </is>
-      </c>
-      <c r="S69" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
+          <t>LeaveGrantBatch</t>
         </is>
       </c>
       <c r="V69" s="14" t="inlineStr">
@@ -9618,7 +9871,7 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Y69" s="14" t="inlineStr">
+      <c r="BC69" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -9627,27 +9880,10 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>LeaveGrantBatch</t>
-        </is>
-      </c>
-      <c r="V70" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="BD70" s="14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="13" t="inlineStr">
-        <is>
           <t>MandatoryLeaveAlertBatch</t>
         </is>
       </c>
-      <c r="Y71" s="14" t="inlineStr">
+      <c r="Y70" s="14" t="inlineStr">
         <is>
           <t>○</t>
         </is>
